--- a/automotive_forms/017_dealership_maintenance_service_feedback_poll--automotive_forms.xlsx
+++ b/automotive_forms/017_dealership_maintenance_service_feedback_poll--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1030,8 +1030,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'service_visit',_'value':_'service_visit'}</t>
+          <t>service_visit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Service Visit', 'value': 'Service Visit'}</t>
+          <t>Service Visit</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'oil_change',_'value':_'oil_change'}</t>
+          <t>oil_change</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Oil Change', 'value': 'Oil Change'}</t>
+          <t>Oil Change</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tire_change',_'value':_'tire_change'}</t>
+          <t>tire_change</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Tire Change', 'value': 'Tire Change'}</t>
+          <t>Tire Change</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John', 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane', 'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'call',_'value':_'call'}</t>
+          <t>call</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Call', 'value': 'Call'}</t>
+          <t>Call</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'message',_'value':_'message'}</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Message', 'value': 'Message'}</t>
+          <t>Message</t>
         </is>
       </c>
     </row>
